--- a/avance_dataset.xlsx
+++ b/avance_dataset.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Documents\magister\propagacion-incendios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7038BC5F-5C26-4CFA-A65B-E4E85A7E4F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECFF6DE-03B2-478C-9B2F-AF482C47425E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8565" yWindow="1830" windowWidth="18090" windowHeight="11295" xr2:uid="{9B1D9094-4E96-4A82-8FE3-ADAC2C531285}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11955" windowHeight="15585" xr2:uid="{9B1D9094-4E96-4A82-8FE3-ADAC2C531285}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="chile" sheetId="2" r:id="rId1"/>
+    <sheet name="EEUU" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
   <si>
     <t>Descargado</t>
   </si>
@@ -121,6 +122,50 @@
 dem_bee_rock_creek.geojson
 dem_haoe_lead.geojson
 dem_picker_flats.geojson</t>
+  </si>
+  <si>
+    <t>Conaf</t>
+  </si>
+  <si>
+    <t>Si, se identificaron los incendios de 2017 (las maquinas) y  2023 (santa ana)</t>
+  </si>
+  <si>
+    <t>Si, se generó un archivo con bandas y coordenadas según areas generadas para las maquimas y santa ana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si, se generó un archivo con bandas y coordenadas según areas generadas para santa ana. No hay info disponible para 2017 </t>
+  </si>
+  <si>
+    <t>No hay info disponible</t>
+  </si>
+  <si>
+    <t>suomi_santa_ana.geojson 
+suomi_las_maquinas.geojson</t>
+  </si>
+  <si>
+    <t>noaa1_santa_ana.geojson</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Puntos con las bandas i04 e i05, su angulo de captura y el nivel de confianza</t>
+  </si>
+  <si>
+    <t>santa_ana_2023.geojson
+las_maquinas.geojson</t>
+  </si>
+  <si>
+    <t>Área en la que se ubicó el incendio</t>
+  </si>
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Observación</t>
+  </si>
+  <si>
+    <t>Falta realizar filtros y calcular temperatura del brillo y FPR</t>
   </si>
 </sst>
 </file>
@@ -144,7 +189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,8 +214,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -193,11 +244,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -213,6 +275,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,17 +617,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D1D7C1-6E65-40B2-B7FE-1A1C1FF61F56}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" customWidth="1"/>
+    <col min="7" max="7" width="33.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2130838B-B70B-49B4-8503-688BEAACF45A}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -576,7 +823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -596,7 +843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -614,7 +861,7 @@
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -632,7 +879,7 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -650,7 +897,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -670,7 +917,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
